--- a/branches/fix/retire-breadcrumb-override/all-profiles.xlsx
+++ b/branches/fix/retire-breadcrumb-override/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T19:17:39+00:00</t>
+    <t>2026-08-05T19:20:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
